--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_42.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2654759.884092499</v>
+        <v>2647892.891143844</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.410716289131</v>
+        <v>286.41071628997</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.410716289131</v>
+        <v>286.41071628997</v>
       </c>
     </row>
     <row r="11">
@@ -672,10 +672,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>266.8560837962714</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
@@ -793,7 +793,7 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
-        <v>178.9682919430025</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>110.705504340989</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -976,19 +976,19 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>199.8180013219744</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>167.1158402638075</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>32.46356367243068</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1222,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>155.0682043885218</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>385</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>147.4295318620689</v>
       </c>
     </row>
     <row r="10">
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751173872</v>
+        <v>21.95645751172477</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1380,13 +1380,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H11" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1456,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V12" t="n">
-        <v>64.51066719152016</v>
+        <v>137.5521873790858</v>
       </c>
       <c r="W12" t="n">
         <v>82.37314290982852</v>
@@ -1513,7 +1513,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1617,13 +1617,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H14" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1684,13 +1684,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>81.10557774904917</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S15" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T15" t="n">
         <v>55.35776521751382</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X17" t="n">
         <v>242.2818334606677</v>
@@ -1921,19 +1921,19 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>81.10557774904923</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>73.04152018756567</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2206,16 +2206,16 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S21" t="n">
-        <v>116.5639999646113</v>
+        <v>197.0736753036327</v>
       </c>
       <c r="T21" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U21" t="n">
-        <v>112.8881222856293</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W21" t="n">
         <v>82.37314290982852</v>
@@ -2334,7 +2334,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X23" t="n">
         <v>242.2818334606677</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>97.2343191717691</v>
       </c>
       <c r="C24" t="n">
-        <v>73.77767497096181</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X24" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y24" t="n">
         <v>49.39139276613435</v>
@@ -2632,7 +2632,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2683,10 +2683,10 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T27" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U27" t="n">
-        <v>112.8881222856293</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V27" t="n">
         <v>64.51066719152016</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C30" t="n">
         <v>11.09991244551929</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S30" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T30" t="n">
         <v>55.35776521751382</v>
@@ -3045,7 +3045,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3090,7 +3090,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>246.2472248460823</v>
+        <v>242.2818334606677</v>
       </c>
       <c r="Y32" t="n">
         <v>161.3174326828064</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
         <v>11.09991244551929</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3151,10 +3151,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S33" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T33" t="n">
         <v>55.35776521751382</v>
@@ -3343,10 +3343,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>75.83998807325922</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S36" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T36" t="n">
         <v>55.35776521751382</v>
@@ -3583,7 +3583,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3592,13 +3592,13 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3753,10 +3753,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H41" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3859,10 +3859,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>197.2737972923793</v>
+        <v>284.2120239427945</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T44" t="n">
         <v>236.6755817285639</v>
@@ -4060,10 +4060,10 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>70.00566530352994</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4114,7 +4114,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>69.86273944538755</v>
@@ -4315,31 +4315,31 @@
         <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
       </c>
       <c r="J2" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="K2" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="L2" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="M2" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="N2" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="O2" t="n">
-        <v>777.6999999999999</v>
+        <v>793.1</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>731.0707066989298</v>
+        <v>601.5717906960114</v>
       </c>
       <c r="C3" t="n">
-        <v>366.3233203903244</v>
+        <v>601.5717906960114</v>
       </c>
       <c r="D3" t="n">
-        <v>366.3233203903244</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="E3" t="n">
-        <v>366.3233203903244</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="F3" t="n">
-        <v>366.3233203903244</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>366.3233203903244</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H3" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4421,31 +4421,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1037.471008962092</v>
+        <v>741.8532800788882</v>
       </c>
       <c r="S3" t="n">
-        <v>970.2346453614745</v>
+        <v>674.6169164782708</v>
       </c>
       <c r="T3" t="n">
-        <v>964.8227613033797</v>
+        <v>669.2050324201761</v>
       </c>
       <c r="U3" t="n">
-        <v>964.6102766971304</v>
+        <v>668.9925478139268</v>
       </c>
       <c r="V3" t="n">
-        <v>783.8342242294511</v>
+        <v>654.3353082265327</v>
       </c>
       <c r="W3" t="n">
-        <v>751.134079876089</v>
+        <v>621.6351638731705</v>
       </c>
       <c r="X3" t="n">
-        <v>731.0707066989298</v>
+        <v>601.5717906960114</v>
       </c>
       <c r="Y3" t="n">
-        <v>731.0707066989298</v>
+        <v>601.5717906960114</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>500.517830983611</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="C4" t="n">
-        <v>626.5198368020468</v>
+        <v>168.986774499966</v>
       </c>
       <c r="D4" t="n">
-        <v>626.5198368020468</v>
+        <v>282.3059186249661</v>
       </c>
       <c r="E4" t="n">
-        <v>626.5198368020468</v>
+        <v>400.1348228363792</v>
       </c>
       <c r="F4" t="n">
-        <v>750.8808093939823</v>
+        <v>524.4957954283146</v>
       </c>
       <c r="G4" t="n">
-        <v>788.2667952520683</v>
+        <v>677.9023613151999</v>
       </c>
       <c r="H4" t="n">
-        <v>957.7833804114658</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="I4" t="n">
-        <v>1178.916259347549</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="J4" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
@@ -4506,25 +4506,25 @@
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="U4" t="n">
-        <v>277.3511926382866</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="V4" t="n">
-        <v>277.3511926382866</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="W4" t="n">
-        <v>277.3511926382866</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="X4" t="n">
-        <v>277.3511926382866</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="Y4" t="n">
-        <v>388.7604933173189</v>
+        <v>68.05025509417312</v>
       </c>
     </row>
     <row r="5">
@@ -4558,7 +4558,7 @@
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="K5" t="n">
         <v>777.6999999999999</v>
@@ -4585,25 +4585,25 @@
         <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4619,16 +4619,16 @@
         <v>897.189519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>545.7373105916365</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="E6" t="n">
-        <v>199.603879054351</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="F6" t="n">
-        <v>199.603879054351</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G6" t="n">
-        <v>199.603879054351</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H6" t="n">
         <v>30.8</v>
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1135.829529740114</v>
+        <v>543.9986667138789</v>
       </c>
       <c r="C7" t="n">
-        <v>1135.829529740114</v>
+        <v>670.0006725323148</v>
       </c>
       <c r="D7" t="n">
-        <v>1135.829529740114</v>
+        <v>783.3198166573148</v>
       </c>
       <c r="E7" t="n">
-        <v>1135.829529740114</v>
+        <v>901.1487208687279</v>
       </c>
       <c r="F7" t="n">
-        <v>1135.829529740114</v>
+        <v>1025.509693460663</v>
       </c>
       <c r="G7" t="n">
-        <v>1135.829529740114</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="H7" t="n">
-        <v>1135.829529740114</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="I7" t="n">
-        <v>1135.829529740114</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="J7" t="n">
-        <v>1496.913270392565</v>
+        <v>1540</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
@@ -4746,22 +4746,22 @@
         <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>256.125934252978</v>
+        <v>169.8012373443611</v>
       </c>
       <c r="U7" t="n">
-        <v>502.6771268912646</v>
+        <v>169.8012373443611</v>
       </c>
       <c r="V7" t="n">
-        <v>701.4985197772105</v>
+        <v>169.8012373443611</v>
       </c>
       <c r="W7" t="n">
-        <v>873.3894380368879</v>
+        <v>169.8012373443611</v>
       </c>
       <c r="X7" t="n">
-        <v>1024.420229061081</v>
+        <v>320.8320283685546</v>
       </c>
       <c r="Y7" t="n">
-        <v>1135.829529740114</v>
+        <v>432.2413290475868</v>
       </c>
     </row>
     <row r="8">
@@ -4786,34 +4786,34 @@
         <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="K8" t="n">
-        <v>411.95</v>
+        <v>411.9499999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>411.95</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>411.95</v>
+        <v>1158.85</v>
       </c>
       <c r="N8" t="n">
-        <v>793.1</v>
+        <v>1158.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="P8" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>522.9578702777202</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="C9" t="n">
-        <v>522.9578702777202</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="D9" t="n">
-        <v>522.9578702777202</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="E9" t="n">
-        <v>522.9578702777202</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="F9" t="n">
-        <v>522.9578702777202</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="G9" t="n">
-        <v>366.3233203903244</v>
+        <v>30.8</v>
       </c>
       <c r="H9" t="n">
         <v>30.8</v>
@@ -4910,16 +4910,16 @@
         <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>575.7213878082415</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>543.0212434548794</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X9" t="n">
-        <v>522.9578702777202</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>522.9578702777202</v>
+        <v>748.2708005266202</v>
       </c>
     </row>
     <row r="10">
@@ -4929,55 +4929,55 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168.9867744999676</v>
+        <v>514.4329432708513</v>
       </c>
       <c r="C10" t="n">
-        <v>168.9867744999676</v>
+        <v>640.4349490892871</v>
       </c>
       <c r="D10" t="n">
-        <v>282.3059186249677</v>
+        <v>753.7540932142872</v>
       </c>
       <c r="E10" t="n">
-        <v>400.1348228363807</v>
+        <v>871.5829974257002</v>
       </c>
       <c r="F10" t="n">
-        <v>524.4957954283162</v>
+        <v>995.9439700176357</v>
       </c>
       <c r="G10" t="n">
-        <v>677.9023613152015</v>
+        <v>1149.350535904521</v>
       </c>
       <c r="H10" t="n">
-        <v>847.418946474599</v>
+        <v>1318.867121063919</v>
       </c>
       <c r="I10" t="n">
-        <v>1068.551825410682</v>
+        <v>1540.000000000002</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063133</v>
+        <v>1540.000000000002</v>
       </c>
       <c r="K10" t="n">
         <v>1540.000000000002</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.821760089154</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1395.971647561326</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.05743011518</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>980.1831229646596</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>689.831711521955</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>360.7011393748862</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R10" t="n">
-        <v>30.79999999998608</v>
+        <v>30.8</v>
       </c>
       <c r="S10" t="n">
         <v>30.8</v>
@@ -4992,13 +4992,13 @@
         <v>30.8</v>
       </c>
       <c r="W10" t="n">
-        <v>168.9867744999676</v>
+        <v>140.2355139013334</v>
       </c>
       <c r="X10" t="n">
-        <v>168.9867744999676</v>
+        <v>291.2663049255269</v>
       </c>
       <c r="Y10" t="n">
-        <v>168.9867744999676</v>
+        <v>402.6756056045592</v>
       </c>
     </row>
     <row r="11">
@@ -5023,10 +5023,10 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H11" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
@@ -5035,10 +5035,10 @@
         <v>44.72</v>
       </c>
       <c r="K11" t="n">
-        <v>137.1709049473328</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L11" t="n">
-        <v>690.5809049473327</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M11" t="n">
         <v>690.5809049473327</v>
@@ -5047,7 +5047,7 @@
         <v>1243.990904947333</v>
       </c>
       <c r="O11" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
         <v>1797.400904947332</v>
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>119.2429040110725</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C12" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D12" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E12" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F12" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G12" t="n">
         <v>44.72</v>
@@ -5147,16 +5147,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>711.3477845844836</v>
+        <v>637.5684712637103</v>
       </c>
       <c r="W12" t="n">
-        <v>628.142589726071</v>
+        <v>554.3632764052976</v>
       </c>
       <c r="X12" t="n">
-        <v>557.5741660438614</v>
+        <v>483.794852723088</v>
       </c>
       <c r="Y12" t="n">
-        <v>154.1485167851398</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="13">
@@ -5260,34 +5260,34 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>64.92117127106515</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>618.3311712710652</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L14" t="n">
-        <v>1171.741171271065</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M14" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N14" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O14" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1508.625837177891</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>1426.70101116875</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>1426.70101116875</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="G15" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="H15" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="I15" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="J15" t="n">
-        <v>1204.524099806763</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K15" t="n">
-        <v>1393.716915901147</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L15" t="n">
-        <v>1665.067377496347</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M15" t="n">
-        <v>1751.147919239206</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N15" t="n">
-        <v>1884.428203846775</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2123.470655530493</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P15" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2036.733538088506</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S15" t="n">
-        <v>1918.992123982838</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T15" t="n">
-        <v>1863.075189419693</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U15" t="n">
-        <v>1812.357654308393</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V15" t="n">
-        <v>1747.195364215948</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W15" t="n">
-        <v>1663.990169357536</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X15" t="n">
-        <v>1593.421745675326</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
-        <v>1543.531449951958</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5457,10 +5457,10 @@
         <v>44.72</v>
       </c>
       <c r="T16" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U16" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V16" t="n">
         <v>521.9574820108303</v>
@@ -5482,49 +5482,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D17" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E17" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G17" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>575.7700000000002</v>
+        <v>598.13</v>
       </c>
       <c r="L17" t="n">
-        <v>1129.18</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M17" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N17" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5545,13 +5545,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X17" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y17" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="18">
@@ -5564,16 +5564,16 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C18" t="n">
-        <v>390.8534315372855</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D18" t="n">
-        <v>390.8534315372855</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>118.4993133207734</v>
       </c>
       <c r="G18" t="n">
         <v>44.72</v>
@@ -5743,22 +5743,22 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N20" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O20" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P20" t="n">
         <v>1797.400904947332</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.93203277325181</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C21" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D21" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E21" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F21" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G21" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H21" t="n">
         <v>44.72</v>
@@ -5849,25 +5849,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>883.1445443513733</v>
+        <v>801.8216399685234</v>
       </c>
       <c r="T21" t="n">
-        <v>827.2276097882281</v>
+        <v>745.9047054053782</v>
       </c>
       <c r="U21" t="n">
-        <v>713.1992034391076</v>
+        <v>695.1871702940784</v>
       </c>
       <c r="V21" t="n">
-        <v>294.5015598113094</v>
+        <v>630.0248802016338</v>
       </c>
       <c r="W21" t="n">
-        <v>211.2963649528968</v>
+        <v>546.8196853432211</v>
       </c>
       <c r="X21" t="n">
-        <v>140.7279412706871</v>
+        <v>476.2512616610114</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.8376455473191</v>
+        <v>426.3609659376434</v>
       </c>
     </row>
     <row r="22">
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C23" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I23" t="n">
         <v>44.72</v>
@@ -5989,13 +5989,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>436.0291130376558</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N23" t="n">
-        <v>690.5809049473327</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O23" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P23" t="n">
         <v>1797.400904947332</v>
@@ -6019,13 +6019,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="24">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C24" t="n">
         <v>44.72</v>
@@ -6101,10 +6101,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="25">
@@ -6114,13 +6114,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E25" t="n">
         <v>1078.695883794875</v>
@@ -6168,22 +6168,22 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6229,10 +6229,10 @@
         <v>946.8779417665908</v>
       </c>
       <c r="N26" t="n">
-        <v>946.8779417665908</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O26" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>1797.400904947332</v>
@@ -6272,19 +6272,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>409.4673863086053</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C27" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D27" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E27" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F27" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G27" t="n">
         <v>44.72</v>
@@ -6326,22 +6326,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U27" t="n">
-        <v>713.1992034391076</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V27" t="n">
-        <v>648.0369133466629</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W27" t="n">
-        <v>564.8317184882503</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X27" t="n">
-        <v>494.2632948060406</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y27" t="n">
-        <v>444.3729990826726</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="28">
@@ -6454,25 +6454,25 @@
         <v>44.72</v>
       </c>
       <c r="J29" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K29" t="n">
-        <v>989.4391130376558</v>
+        <v>44.72</v>
       </c>
       <c r="L29" t="n">
-        <v>1542.849113037656</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M29" t="n">
-        <v>1542.849113037656</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N29" t="n">
-        <v>2096.259113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O29" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P29" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6509,16 +6509,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F30" t="n">
         <v>44.72</v>
@@ -6557,28 +6557,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S30" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T30" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U30" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V30" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W30" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X30" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y30" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="31">
@@ -6667,46 +6667,46 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C32" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D32" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E32" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F32" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H32" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>64.92117127106526</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>1129.18</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N32" t="n">
-        <v>1682.59</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>2236</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P32" t="n">
         <v>2236</v>
@@ -6733,10 +6733,10 @@
         <v>974.4145997704354</v>
       </c>
       <c r="X32" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y32" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="33">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C33" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D33" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E33" t="n">
         <v>44.72</v>
@@ -6794,28 +6794,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R33" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S33" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T33" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U33" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V33" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W33" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X33" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y33" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="34">
@@ -6931,22 +6931,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L35" t="n">
-        <v>1542.849113037656</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M35" t="n">
-        <v>1542.849113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N35" t="n">
-        <v>2096.259113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C36" t="n">
-        <v>396.1722089875784</v>
+        <v>44.72</v>
       </c>
       <c r="D36" t="n">
         <v>44.72</v>
@@ -7031,28 +7031,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="37">
@@ -7116,10 +7116,10 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V37" t="n">
         <v>521.9574820108303</v>
@@ -7165,25 +7165,25 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K38" t="n">
-        <v>989.4391130376558</v>
+        <v>44.72</v>
       </c>
       <c r="L38" t="n">
-        <v>1542.849113037656</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M38" t="n">
-        <v>1542.849113037656</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N38" t="n">
-        <v>2096.259113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O38" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
@@ -7226,19 +7226,19 @@
         <v>461.5662247731743</v>
       </c>
       <c r="D39" t="n">
-        <v>461.5662247731743</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E39" t="n">
-        <v>461.5662247731743</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F39" t="n">
-        <v>461.5662247731743</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7299,19 +7299,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F40" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G40" t="n">
         <v>1257.463422273695</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7396,7 +7396,7 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
@@ -7408,13 +7408,13 @@
         <v>598.13</v>
       </c>
       <c r="L41" t="n">
-        <v>733.1420762183976</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="M41" t="n">
+        <v>690.5809049473327</v>
+      </c>
+      <c r="N41" t="n">
         <v>1243.990904947333</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
         <v>1797.400904947332</v>
@@ -7457,19 +7457,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>384.9618669904511</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G42" t="n">
         <v>44.72</v>
@@ -7502,31 +7502,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1136.841549130715</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>937.5750872192206</v>
+        <v>913.0695679010663</v>
       </c>
       <c r="S42" t="n">
-        <v>819.8336731135525</v>
+        <v>795.3281537953983</v>
       </c>
       <c r="T42" t="n">
-        <v>763.9167385504073</v>
+        <v>739.4112192322531</v>
       </c>
       <c r="U42" t="n">
-        <v>713.1992034391076</v>
+        <v>688.6936841209533</v>
       </c>
       <c r="V42" t="n">
-        <v>648.0369133466629</v>
+        <v>623.5313940285087</v>
       </c>
       <c r="W42" t="n">
-        <v>564.8317184882503</v>
+        <v>540.3261991700961</v>
       </c>
       <c r="X42" t="n">
-        <v>494.2632948060407</v>
+        <v>469.7577754878864</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>419.8674797645184</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J43" t="n">
         <v>1860.696627021627</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="44">
@@ -7615,49 +7615,49 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K44" t="n">
-        <v>989.4391130376558</v>
+        <v>598.13</v>
       </c>
       <c r="L44" t="n">
-        <v>1542.849113037656</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M44" t="n">
-        <v>1542.849113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
-        <v>1542.849113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7666,25 +7666,25 @@
         <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,16 +7694,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>115.4327932358888</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
         <v>44.72</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>648.036913346663</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>404.4874506895348</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>385.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>542.2671287719298</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>404.4874506895348</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>913.7065720867616</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>542.2671287719298</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,22 +8678,22 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>93.38475247205329</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>55.44822975121676</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>141.1524110730753</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9404,7 +9404,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>300.4011642636528</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9632,16 +9632,16 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>734.371980200822</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>629.2478695740924</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P23" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9872,13 +9872,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O26" t="n">
-        <v>370.361973797064</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P26" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>313.9750954005603</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,13 +10334,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>20.40522350612653</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10352,7 +10352,7 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q32" t="n">
         <v>172.8226843274854</v>
@@ -10574,25 +10574,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>211.4002806471673</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>141.4394711137563</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11051,16 +11051,16 @@
         <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>136.375834564038</v>
+        <v>93.38475247205326</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>313.9750954005603</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646040439</v>
+        <v>1.591170646054422</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2699789.488256875</v>
+        <v>2699789.488256874</v>
       </c>
     </row>
     <row r="5">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4471143.642904327</v>
+        <v>4471143.642904326</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5352707.571137143</v>
+        <v>5352707.571137142</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6234271.499369957</v>
+        <v>6234271.499369955</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7115835.427602769</v>
+        <v>7115835.427602768</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7997399.355835582</v>
+        <v>7997399.355835581</v>
       </c>
     </row>
     <row r="11">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9760527.212301213</v>
+        <v>9760527.212301211</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10642091.14053404</v>
+        <v>10642091.14053403</v>
       </c>
     </row>
     <row r="14">
@@ -26278,19 +26278,19 @@
         <v>1322305.794848944</v>
       </c>
       <c r="E2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="F2" t="n">
         <v>1322345.892349224</v>
       </c>
       <c r="G2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="H2" t="n">
         <v>1322345.892349225</v>
       </c>
       <c r="I2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="J2" t="n">
         <v>1322345.892349225</v>
@@ -26308,10 +26308,10 @@
         <v>1322345.892349225</v>
       </c>
       <c r="O2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="P2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.3728533792</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941388</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983396</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380801</v>
+        <v>531178.6502511878</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984991</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>558836.0699494343</v>
+        <v>557320.2142611184</v>
       </c>
       <c r="C6" t="n">
-        <v>696414.0500832488</v>
+        <v>694898.1943949332</v>
       </c>
       <c r="D6" t="n">
-        <v>698474.8219955644</v>
+        <v>696958.9663072488</v>
       </c>
       <c r="E6" t="n">
-        <v>374592.4891226889</v>
+        <v>372850.6393095817</v>
       </c>
       <c r="F6" t="n">
-        <v>717783.3844681933</v>
+        <v>716041.5346550855</v>
       </c>
       <c r="G6" t="n">
-        <v>719728.9609363785</v>
+        <v>717987.111123272</v>
       </c>
       <c r="H6" t="n">
-        <v>721677.2377536808</v>
+        <v>719935.3879405727</v>
       </c>
       <c r="I6" t="n">
-        <v>723628.2343970403</v>
+        <v>721886.3845839332</v>
       </c>
       <c r="J6" t="n">
-        <v>310061.9705986659</v>
+        <v>308320.1207855587</v>
       </c>
       <c r="K6" t="n">
-        <v>727538.4663508852</v>
+        <v>725796.6165377776</v>
       </c>
       <c r="L6" t="n">
-        <v>729497.741911144</v>
+        <v>727755.8920980365</v>
       </c>
       <c r="M6" t="n">
-        <v>670211.8178071245</v>
+        <v>668469.9679940167</v>
       </c>
       <c r="N6" t="n">
-        <v>733424.7148419777</v>
+        <v>731682.8650288703</v>
       </c>
       <c r="O6" t="n">
-        <v>455392.4540997149</v>
+        <v>453650.6042866086</v>
       </c>
       <c r="P6" t="n">
-        <v>737363.0569507253</v>
+        <v>735621.2071376182</v>
       </c>
     </row>
   </sheetData>
@@ -26984,10 +26984,10 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -26999,13 +26999,13 @@
         <v>350</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>-0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -27039,10 +27039,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
@@ -27091,7 +27091,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27451,10 +27451,10 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27515,10 +27515,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27530,10 +27530,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>280.4177134961079</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27572,7 +27572,7 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>235.5423752485177</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27591,22 +27591,22 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C4" t="n">
+        <v>374.6813268559163</v>
+      </c>
+      <c r="D4" t="n">
         <v>400</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>400</v>
-      </c>
-      <c r="D4" t="n">
-        <v>285.5362180555555</v>
-      </c>
-      <c r="E4" t="n">
-        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>282.8074949204047</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27618,7 +27618,7 @@
         <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27670,7 +27670,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
         <v>400</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27755,19 +27755,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>148.1196855757283</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>165.0522469226136</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27828,22 +27828,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
         <v>228.7711261016186</v>
@@ -27855,7 +27855,7 @@
         <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>332.0427228995622</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,16 +27882,16 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>312.8033364559425</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -28001,10 +28001,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>170.6713314865055</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28046,7 +28046,7 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>29.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>251.9618609040654</v>
       </c>
     </row>
     <row r="10">
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -28089,10 +28089,10 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028695</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
         <v>210.0245665062577</v>
@@ -28128,13 +28128,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>365.9554103437275</v>
+        <v>336.9137329713697</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28159,13 +28159,13 @@
         <v>350</v>
       </c>
       <c r="G11" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H11" t="n">
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28235,10 +28235,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>263.0617733495849</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
         <v>332.1680871864211</v>
@@ -28283,7 +28283,7 @@
         <v>350</v>
       </c>
       <c r="V12" t="n">
-        <v>350</v>
+        <v>276.9584798124343</v>
       </c>
       <c r="W12" t="n">
         <v>350</v>
@@ -28292,7 +28292,7 @@
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -28396,13 +28396,13 @@
         <v>350</v>
       </c>
       <c r="G14" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H14" t="n">
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28463,13 +28463,13 @@
         <v>350</v>
       </c>
       <c r="C15" t="n">
-        <v>279.9943346964701</v>
+        <v>350</v>
       </c>
       <c r="D15" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
@@ -28508,10 +28508,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T15" t="n">
         <v>350</v>
@@ -28593,13 +28593,13 @@
         <v>350</v>
       </c>
       <c r="T16" t="n">
+        <v>350</v>
+      </c>
+      <c r="U16" t="n">
+        <v>350</v>
+      </c>
+      <c r="V16" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U16" t="n">
-        <v>350</v>
-      </c>
-      <c r="V16" t="n">
-        <v>350</v>
       </c>
       <c r="W16" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28681,7 +28681,7 @@
         <v>350</v>
       </c>
       <c r="W17" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X17" t="n">
         <v>350</v>
@@ -28700,19 +28700,19 @@
         <v>350</v>
       </c>
       <c r="C18" t="n">
-        <v>279.99433469647</v>
+        <v>350</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>325.7395358750273</v>
+        <v>252.6980156874617</v>
       </c>
       <c r="H18" t="n">
         <v>332.1680871864211</v>
@@ -28952,7 +28952,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>217.1263858913485</v>
@@ -28985,16 +28985,16 @@
         <v>350</v>
       </c>
       <c r="S21" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="T21" t="n">
         <v>350</v>
       </c>
       <c r="U21" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W21" t="n">
         <v>350</v>
@@ -29113,7 +29113,7 @@
         <v>350</v>
       </c>
       <c r="I23" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>350</v>
       </c>
       <c r="W23" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X23" t="n">
         <v>350</v>
@@ -29171,10 +29171,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="C24" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29237,7 +29237,7 @@
         <v>350</v>
       </c>
       <c r="X24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>350</v>
@@ -29259,52 +29259,52 @@
         <v>350</v>
       </c>
       <c r="E25" t="n">
+        <v>350</v>
+      </c>
+      <c r="F25" t="n">
+        <v>350</v>
+      </c>
+      <c r="G25" t="n">
+        <v>350</v>
+      </c>
+      <c r="H25" t="n">
+        <v>350</v>
+      </c>
+      <c r="I25" t="n">
+        <v>350</v>
+      </c>
+      <c r="J25" t="n">
+        <v>350</v>
+      </c>
+      <c r="K25" t="n">
+        <v>350</v>
+      </c>
+      <c r="L25" t="n">
+        <v>350</v>
+      </c>
+      <c r="M25" t="n">
+        <v>350</v>
+      </c>
+      <c r="N25" t="n">
+        <v>350</v>
+      </c>
+      <c r="O25" t="n">
+        <v>350</v>
+      </c>
+      <c r="P25" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>350</v>
+      </c>
+      <c r="R25" t="n">
+        <v>350</v>
+      </c>
+      <c r="S25" t="n">
+        <v>350</v>
+      </c>
+      <c r="T25" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="F25" t="n">
-        <v>350</v>
-      </c>
-      <c r="G25" t="n">
-        <v>350</v>
-      </c>
-      <c r="H25" t="n">
-        <v>350</v>
-      </c>
-      <c r="I25" t="n">
-        <v>350</v>
-      </c>
-      <c r="J25" t="n">
-        <v>350</v>
-      </c>
-      <c r="K25" t="n">
-        <v>350</v>
-      </c>
-      <c r="L25" t="n">
-        <v>350</v>
-      </c>
-      <c r="M25" t="n">
-        <v>350</v>
-      </c>
-      <c r="N25" t="n">
-        <v>350</v>
-      </c>
-      <c r="O25" t="n">
-        <v>350</v>
-      </c>
-      <c r="P25" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>350</v>
-      </c>
-      <c r="R25" t="n">
-        <v>350</v>
-      </c>
-      <c r="S25" t="n">
-        <v>350</v>
-      </c>
-      <c r="T25" t="n">
-        <v>350</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
@@ -29411,7 +29411,7 @@
         <v>350</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -29423,7 +29423,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>325.7395358750273</v>
+        <v>263.0617733495849</v>
       </c>
       <c r="H27" t="n">
         <v>332.1680871864211</v>
@@ -29462,10 +29462,10 @@
         <v>350</v>
       </c>
       <c r="T27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -29645,7 +29645,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C30" t="n">
         <v>350</v>
@@ -29657,7 +29657,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>276.9584798124343</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>325.7395358750273</v>
@@ -29693,10 +29693,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T30" t="n">
         <v>350</v>
@@ -29824,7 +29824,7 @@
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29869,7 +29869,7 @@
         <v>350</v>
       </c>
       <c r="X32" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="Y32" t="n">
         <v>350</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C33" t="n">
         <v>350</v>
@@ -29891,7 +29891,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>279.9943346964701</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
@@ -29930,10 +29930,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T33" t="n">
         <v>350</v>
@@ -30122,10 +30122,10 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>285.2599243722601</v>
+        <v>350</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30167,10 +30167,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T36" t="n">
         <v>350</v>
@@ -30252,13 +30252,13 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
       </c>
       <c r="V37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W37" t="n">
         <v>350</v>
@@ -30362,7 +30362,7 @@
         <v>350</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>260.9994602472874</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30371,13 +30371,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>136.6167105523271</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30450,46 +30450,46 @@
         <v>350</v>
       </c>
       <c r="G40" t="n">
+        <v>350</v>
+      </c>
+      <c r="H40" t="n">
+        <v>350</v>
+      </c>
+      <c r="I40" t="n">
+        <v>350</v>
+      </c>
+      <c r="J40" t="n">
+        <v>350</v>
+      </c>
+      <c r="K40" t="n">
+        <v>350</v>
+      </c>
+      <c r="L40" t="n">
+        <v>350</v>
+      </c>
+      <c r="M40" t="n">
+        <v>350</v>
+      </c>
+      <c r="N40" t="n">
+        <v>350</v>
+      </c>
+      <c r="O40" t="n">
+        <v>350</v>
+      </c>
+      <c r="P40" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>350</v>
+      </c>
+      <c r="R40" t="n">
+        <v>350</v>
+      </c>
+      <c r="S40" t="n">
+        <v>350</v>
+      </c>
+      <c r="T40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="H40" t="n">
-        <v>350</v>
-      </c>
-      <c r="I40" t="n">
-        <v>350</v>
-      </c>
-      <c r="J40" t="n">
-        <v>350</v>
-      </c>
-      <c r="K40" t="n">
-        <v>350</v>
-      </c>
-      <c r="L40" t="n">
-        <v>350</v>
-      </c>
-      <c r="M40" t="n">
-        <v>350</v>
-      </c>
-      <c r="N40" t="n">
-        <v>350</v>
-      </c>
-      <c r="O40" t="n">
-        <v>350</v>
-      </c>
-      <c r="P40" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>350</v>
-      </c>
-      <c r="R40" t="n">
-        <v>350</v>
-      </c>
-      <c r="S40" t="n">
-        <v>350</v>
-      </c>
-      <c r="T40" t="n">
-        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30532,10 +30532,10 @@
         <v>350</v>
       </c>
       <c r="H41" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30608,7 +30608,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>332.1680871864211</v>
@@ -30638,10 +30638,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>110.4015025650371</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>350</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
@@ -30696,7 +30696,7 @@
         <v>350</v>
       </c>
       <c r="J43" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30802,7 +30802,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T44" t="n">
         <v>350</v>
@@ -30839,10 +30839,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>269.6305770343469</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>325.7395358750273</v>
@@ -30878,7 +30878,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
@@ -30893,7 +30893,7 @@
         <v>350</v>
       </c>
       <c r="W45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>385</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,22 +34877,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>101.9560802078716</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>37.76362207887472</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
@@ -34904,7 +34904,7 @@
         <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -35114,22 +35114,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -35141,7 +35141,7 @@
         <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>43.52194909841921</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,16 +35168,16 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>102.7787699496848</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>385</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>369.4444444444443</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>385</v>
-      </c>
-      <c r="O8" t="n">
-        <v>385</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>369.4444444444445</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
@@ -35375,10 +35375,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.405654492915309e-11</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35414,13 +35414,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>139.5826005050178</v>
+        <v>110.54092313266</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,22 +35457,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>93.38475247205329</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>20.40522350612643</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35879,13 +35879,13 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V16" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W16" t="n">
         <v>123.6271901612903</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>141.1524110730753</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36183,7 +36183,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36411,16 +36411,16 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>257.1230221309867</v>
+        <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36545,7 +36545,7 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E25" t="n">
-        <v>61.23042579717762</v>
+        <v>69.01909516304346</v>
       </c>
       <c r="F25" t="n">
         <v>75.61714403225807</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
@@ -36651,13 +36651,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O26" t="n">
-        <v>300.1141042229716</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>141.1524110730749</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37113,13 +37113,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>20.40522350612653</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
@@ -37131,7 +37131,7 @@
         <v>559</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37353,25 +37353,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>300.1141042229715</v>
+      </c>
+      <c r="M35" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>559</v>
       </c>
-      <c r="L35" t="n">
-        <v>559</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>559</v>
-      </c>
-      <c r="O35" t="n">
-        <v>141.1524110730749</v>
-      </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37538,13 +37538,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V37" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W37" t="n">
         <v>123.6271901612903</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
         <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P38" t="n">
-        <v>141.1524110730749</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37736,7 +37736,7 @@
         <v>75.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>97.1674577926042</v>
+        <v>104.95612715847</v>
       </c>
       <c r="H40" t="n">
         <v>121.2288738983814</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37830,16 +37830,16 @@
         <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>136.375834564038</v>
+        <v>93.38475247205326</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K43" t="n">
         <v>61.47922619885696</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
+        <v>136.375834564038</v>
+      </c>
+      <c r="M44" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N44" t="n">
         <v>559</v>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
       <c r="O44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>141.1524110730749</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
